--- a/data/satisfaction_detail/2026/1-2月/商务简餐.xlsx
+++ b/data/satisfaction_detail/2026/1-2月/商务简餐.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>9.59</v>
+        <v>9.58</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>10</v>
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>9.84</v>
+        <v>9.85</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>10</v>
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.17</v>
       </c>
       <c r="C11" s="3" t="n">
         <v>10</v>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>9.84</v>
+        <v>9.77</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>10</v>
@@ -628,7 +628,7 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>9.359999999999999</v>
+        <v>9.34</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>10</v>
